--- a/templates/china/template.xlsx
+++ b/templates/china/template.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CodeUp-工资哥All项目\转换\templates\china\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
@@ -3095,7 +3100,7 @@
       <c r="E10" s="101"/>
       <c r="F10" s="107">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46227</v>
       </c>
       <c r="G10" s="96"/>
     </row>

--- a/templates/china/template.xlsx
+++ b/templates/china/template.xlsx
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="154">
   <si>
     <r>
       <rPr>
@@ -132,9 +132,6 @@
     <t>Company name:</t>
   </si>
   <si>
-    <t>Hermetic Solutions Group, Inc</t>
-  </si>
-  <si>
     <t>Currency</t>
   </si>
   <si>
@@ -144,19 +141,10 @@
     <t>Client ID:</t>
   </si>
   <si>
-    <t>CUS15253</t>
-  </si>
-  <si>
     <t>Invoice number</t>
   </si>
   <si>
-    <t>PN-CUS15253-031820261</t>
-  </si>
-  <si>
     <t>Address:</t>
-  </si>
-  <si>
-    <t>Eight Neshaminy Interplex,Suite 221, Trevose. PA 19053</t>
   </si>
   <si>
     <t>Invoice date</t>
@@ -234,6 +222,9 @@
     <t>3. This is a computer generated document.  No Signature required.</t>
   </si>
   <si>
+    <t>China</t>
+  </si>
+  <si>
     <t>Pay Period</t>
   </si>
   <si>
@@ -421,9 +412,6 @@
     <t>(RMB)</t>
   </si>
   <si>
-    <t>CPT</t>
-  </si>
-  <si>
     <t>Other Fee</t>
   </si>
   <si>
@@ -434,6 +422,9 @@
   </si>
   <si>
     <t xml:space="preserve">Invoice adjustment </t>
+  </si>
+  <si>
+    <t>China EE</t>
   </si>
   <si>
     <t>EE</t>
@@ -500,7 +491,7 @@
     <t>EOR/PEO(CNY)</t>
   </si>
   <si>
-    <t>CUS1525</t>
+    <t>=China!C9</t>
   </si>
   <si>
     <t>工号</t>
@@ -3056,64 +3047,51 @@
       <c r="A8" s="101" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="102" t="s">
-        <v>6</v>
-      </c>
+      <c r="B8" s="102"/>
       <c r="C8" s="103"/>
       <c r="D8" s="101" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E8" s="101"/>
       <c r="F8" s="102" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G8" s="104"/>
     </row>
     <row r="9" s="88" customFormat="1" ht="13" customHeight="1" spans="1:8">
       <c r="A9" s="101" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="102" t="s">
-        <v>10</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B9" s="102"/>
       <c r="C9" s="105"/>
       <c r="D9" s="101" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E9" s="101"/>
-      <c r="F9" s="102" t="s">
-        <v>12</v>
-      </c>
+      <c r="F9" s="102"/>
       <c r="G9" s="104"/>
     </row>
     <row r="10" s="87" customFormat="1" ht="13" customHeight="1" spans="1:8">
       <c r="A10" s="101" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="106" t="s">
-        <v>14</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B10" s="106"/>
       <c r="C10" s="105"/>
       <c r="D10" s="101" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E10" s="101"/>
-      <c r="F10" s="107">
-        <f ca="1">TODAY()</f>
-        <v>46227</v>
-      </c>
+      <c r="F10" s="107"/>
       <c r="G10" s="96"/>
     </row>
     <row r="11" s="88" customFormat="1" ht="12" customHeight="1" spans="1:8">
       <c r="A11" s="108"/>
       <c r="B11" s="106"/>
       <c r="D11" s="101" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E11" s="101"/>
-      <c r="F11" s="107">
-        <v>46105</v>
-      </c>
+      <c r="F11" s="107"/>
       <c r="G11" s="104"/>
     </row>
     <row r="12" s="87" customFormat="1" ht="12" customHeight="1" spans="1:8">
@@ -3127,7 +3105,7 @@
     <row r="13" ht="12"/>
     <row r="14" s="89" customFormat="1" ht="28" customHeight="1" spans="1:8">
       <c r="A14" s="111" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B14" s="112"/>
       <c r="C14" s="112"/>
@@ -3137,13 +3115,13 @@
         <v>Amount (RMB)</v>
       </c>
       <c r="F14" s="113" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G14" s="114"/>
     </row>
     <row r="15" s="90" customFormat="1" ht="16" customHeight="1" spans="1:8">
       <c r="A15" s="115" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B15" s="116"/>
       <c r="C15" s="116"/>
@@ -3161,7 +3139,7 @@
     <row r="16" s="91" customFormat="1" ht="12.75" spans="1:8">
       <c r="A16" s="120" t="str">
         <f ca="1">"- Labor cost for "&amp;China!B9&amp;"  -  "&amp;MONTH(China!B2)&amp;"-"&amp;YEAR(China!B2)</f>
-        <v>- Labor cost for CPT  -  7-2026</v>
+        <v>- Labor cost for   -  7-2026</v>
       </c>
       <c r="B16" s="121"/>
       <c r="C16" s="121"/>
@@ -3179,7 +3157,7 @@
     <row r="17" ht="12.75" spans="1:7">
       <c r="A17" s="120" t="str">
         <f>"- "&amp;+"Expense claim for "&amp;China!B9</f>
-        <v>- Expense claim for CPT</v>
+        <v>- Expense claim for </v>
       </c>
       <c r="B17" s="121"/>
       <c r="C17" s="121"/>
@@ -3214,18 +3192,18 @@
     </row>
     <row r="20" s="92" customFormat="1" ht="16" customHeight="1" spans="1:7">
       <c r="A20" s="115" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B20" s="116"/>
       <c r="C20" s="116"/>
       <c r="D20" s="116"/>
       <c r="E20" s="117">
         <f>SUM(E21:E22)</f>
-        <v>2549.4</v>
+        <v>2349.4</v>
       </c>
       <c r="F20" s="131">
         <f>SUM(F21:F22)</f>
-        <v>368.943560057887</v>
+        <v>340</v>
       </c>
       <c r="G20" s="132"/>
     </row>
@@ -3239,11 +3217,11 @@
       <c r="D21" s="134"/>
       <c r="E21" s="130">
         <f>China!G9</f>
-        <v>2549.4</v>
+        <v>2349.4</v>
       </c>
       <c r="F21" s="123">
         <f>E21/$B$29</f>
-        <v>368.943560057887</v>
+        <v>340</v>
       </c>
       <c r="G21" s="125"/>
     </row>
@@ -3258,7 +3236,7 @@
     </row>
     <row r="23" s="92" customFormat="1" ht="16" customHeight="1" spans="1:7">
       <c r="A23" s="115" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B23" s="116"/>
       <c r="C23" s="116"/>
@@ -3276,7 +3254,7 @@
     <row r="24" ht="12.75" spans="1:7">
       <c r="A24" s="133" t="str">
         <f ca="1">"- "&amp;+"Deposit  for "&amp;China!B9&amp;"  -  "&amp;MONTH(China!B2)&amp;"-"&amp;YEAR(China!B2)</f>
-        <v>- Deposit  for CPT  -  7-2026</v>
+        <v>- Deposit  for   -  7-2026</v>
       </c>
       <c r="B24" s="134"/>
       <c r="C24" s="134"/>
@@ -3302,18 +3280,18 @@
     </row>
     <row r="26" s="90" customFormat="1" ht="15" spans="1:7">
       <c r="A26" s="139" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B26" s="140"/>
       <c r="C26" s="140"/>
       <c r="D26" s="140"/>
       <c r="E26" s="141">
         <f>E15+E20+E23</f>
-        <v>2549.4</v>
+        <v>2349.4</v>
       </c>
       <c r="F26" s="142">
         <f>F15+F20+F23</f>
-        <v>368.943560057887</v>
+        <v>340</v>
       </c>
       <c r="G26" s="119"/>
     </row>
@@ -3345,12 +3323,12 @@
       </c>
       <c r="C29" s="145"/>
       <c r="D29" s="150" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E29" s="151"/>
       <c r="F29" s="152">
         <f>F26</f>
-        <v>368.943560057887</v>
+        <v>340</v>
       </c>
       <c r="G29" s="125"/>
     </row>
@@ -3359,7 +3337,7 @@
       <c r="B30" s="153"/>
       <c r="C30" s="145"/>
       <c r="D30" s="154" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E30" s="155"/>
       <c r="F30" s="156">
@@ -3373,7 +3351,7 @@
       <c r="B31" s="153"/>
       <c r="C31" s="145"/>
       <c r="D31" s="154" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E31" s="155"/>
       <c r="F31" s="156">
@@ -3387,7 +3365,7 @@
       <c r="B32" s="153"/>
       <c r="C32" s="145"/>
       <c r="D32" s="154" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E32" s="155"/>
       <c r="F32" s="156">
@@ -3401,7 +3379,7 @@
       <c r="B33" s="153"/>
       <c r="C33" s="157"/>
       <c r="D33" s="158" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E33" s="159"/>
       <c r="F33" s="160">
@@ -3415,12 +3393,12 @@
       <c r="B34" s="153"/>
       <c r="C34" s="145"/>
       <c r="D34" s="161" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E34" s="162"/>
       <c r="F34" s="163">
         <f>SUM(F29:F33)</f>
-        <v>403.943560057887</v>
+        <v>375</v>
       </c>
       <c r="G34" s="125"/>
     </row>
@@ -3429,7 +3407,7 @@
       <c r="B35" s="153"/>
       <c r="C35" s="145"/>
       <c r="D35" s="164" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E35" s="165"/>
       <c r="F35" s="163">
@@ -3443,12 +3421,12 @@
       <c r="B36" s="166"/>
       <c r="C36" s="145"/>
       <c r="D36" s="167" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E36" s="168"/>
       <c r="F36" s="169">
         <f>SUM(F34:F35)</f>
-        <v>403.943560057887</v>
+        <v>375</v>
       </c>
       <c r="G36" s="125"/>
       <c r="H36" s="170"/>
@@ -3476,7 +3454,7 @@
     </row>
     <row r="40" ht="19" customHeight="1" spans="1:8">
       <c r="A40" s="171" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B40" s="171"/>
       <c r="C40" s="171"/>
@@ -3486,24 +3464,24 @@
     </row>
     <row r="41" ht="61" customHeight="1" spans="1:8">
       <c r="A41" s="172" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B41" s="172"/>
       <c r="C41" s="173"/>
       <c r="D41" s="174" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E41" s="172"/>
       <c r="F41" s="172"/>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="93" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="43" ht="11.15" customHeight="1" spans="1:8">
       <c r="A43" s="90" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B43" s="90"/>
       <c r="C43" s="90"/>
@@ -3513,12 +3491,12 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="90" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="90" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -3608,15 +3586,14 @@
     <col min="62" max="16384" width="9.09166666666667" style="33"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.5" spans="1:61">
-      <c r="A1" s="32" t="str">
-        <f ca="1">MID(CELL("filename",A1),FIND("]",CELL("filename",A1))+1,256)</f>
-        <v>China</v>
+    <row r="1" spans="1:61">
+      <c r="A1" s="32" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="2" ht="13.5" spans="1:61">
       <c r="A2" s="34" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B2" s="68">
         <f ca="1">EOMONTH(TODAY(),-1)+1</f>
@@ -3627,26 +3604,26 @@
         <v>46234</v>
       </c>
       <c r="E2" s="36" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" s="30" customFormat="1" ht="13" customHeight="1" spans="1:61">
       <c r="A3" s="34"/>
       <c r="B3" s="35"/>
       <c r="E3" s="69" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F3" s="70" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G3" s="71" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H3" s="72"/>
       <c r="I3" s="72"/>
       <c r="J3" s="73"/>
       <c r="K3" s="41" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="L3" s="42"/>
       <c r="M3" s="42"/>
@@ -3680,7 +3657,7 @@
       <c r="AO3" s="42"/>
       <c r="AP3" s="42"/>
       <c r="AQ3" s="41" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="AR3" s="42"/>
       <c r="AS3" s="42"/>
@@ -3694,183 +3671,183 @@
       <c r="BA3" s="42"/>
       <c r="BB3" s="74"/>
       <c r="BC3" s="41" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="BD3" s="42"/>
       <c r="BE3" s="74"/>
       <c r="BF3" s="43" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="BG3" s="43"/>
       <c r="BH3" s="43"/>
       <c r="BI3" s="75" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" s="30" customFormat="1" ht="51.75" spans="1:61">
       <c r="E4" s="47"/>
       <c r="F4" s="48"/>
       <c r="G4" s="48" t="s">
+        <v>45</v>
+      </c>
+      <c r="H4" s="49" t="s">
+        <v>46</v>
+      </c>
+      <c r="I4" s="49" t="s">
+        <v>47</v>
+      </c>
+      <c r="J4" s="49" t="s">
         <v>48</v>
       </c>
-      <c r="H4" s="49" t="s">
+      <c r="K4" s="48" t="s">
+        <v>45</v>
+      </c>
+      <c r="L4" s="49" t="s">
         <v>49</v>
       </c>
-      <c r="I4" s="49" t="s">
+      <c r="M4" s="49" t="s">
         <v>50</v>
       </c>
-      <c r="J4" s="49" t="s">
+      <c r="N4" s="49" t="s">
         <v>51</v>
       </c>
-      <c r="K4" s="48" t="s">
-        <v>48</v>
-      </c>
-      <c r="L4" s="49" t="s">
+      <c r="O4" s="49" t="s">
         <v>52</v>
       </c>
-      <c r="M4" s="49" t="s">
+      <c r="P4" s="49" t="s">
         <v>53</v>
       </c>
-      <c r="N4" s="49" t="s">
+      <c r="Q4" s="49" t="s">
         <v>54</v>
       </c>
-      <c r="O4" s="49" t="s">
+      <c r="R4" s="49" t="s">
         <v>55</v>
       </c>
-      <c r="P4" s="49" t="s">
+      <c r="S4" s="49" t="s">
         <v>56</v>
       </c>
-      <c r="Q4" s="49" t="s">
+      <c r="T4" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="R4" s="49" t="s">
+      <c r="U4" s="49" t="s">
         <v>58</v>
       </c>
-      <c r="S4" s="49" t="s">
+      <c r="V4" s="49" t="s">
         <v>59</v>
       </c>
-      <c r="T4" s="49" t="s">
+      <c r="W4" s="49" t="s">
         <v>60</v>
       </c>
-      <c r="U4" s="49" t="s">
+      <c r="X4" s="49" t="s">
         <v>61</v>
       </c>
-      <c r="V4" s="49" t="s">
+      <c r="Y4" s="49" t="s">
         <v>62</v>
       </c>
-      <c r="W4" s="49" t="s">
+      <c r="Z4" s="49" t="s">
         <v>63</v>
       </c>
-      <c r="X4" s="49" t="s">
+      <c r="AA4" s="49" t="s">
         <v>64</v>
       </c>
-      <c r="Y4" s="49" t="s">
+      <c r="AB4" s="49" t="s">
         <v>65</v>
       </c>
-      <c r="Z4" s="49" t="s">
+      <c r="AC4" s="49" t="s">
         <v>66</v>
       </c>
-      <c r="AA4" s="49" t="s">
+      <c r="AD4" s="49" t="s">
         <v>67</v>
       </c>
-      <c r="AB4" s="49" t="s">
+      <c r="AE4" s="49" t="s">
         <v>68</v>
       </c>
-      <c r="AC4" s="49" t="s">
+      <c r="AF4" s="49" t="s">
         <v>69</v>
       </c>
-      <c r="AD4" s="49" t="s">
+      <c r="AG4" s="50" t="s">
         <v>70</v>
       </c>
-      <c r="AE4" s="49" t="s">
+      <c r="AH4" s="50" t="s">
         <v>71</v>
       </c>
-      <c r="AF4" s="49" t="s">
+      <c r="AI4" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="AG4" s="50" t="s">
+      <c r="AJ4" s="50" t="s">
         <v>73</v>
       </c>
-      <c r="AH4" s="50" t="s">
+      <c r="AK4" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="AI4" s="50" t="s">
+      <c r="AL4" s="50" t="s">
         <v>75</v>
       </c>
-      <c r="AJ4" s="50" t="s">
+      <c r="AM4" s="50" t="s">
         <v>76</v>
       </c>
-      <c r="AK4" s="50" t="s">
+      <c r="AN4" s="50" t="s">
         <v>77</v>
       </c>
-      <c r="AL4" s="50" t="s">
+      <c r="AO4" s="50" t="s">
         <v>78</v>
       </c>
-      <c r="AM4" s="50" t="s">
+      <c r="AP4" s="50" t="s">
         <v>79</v>
       </c>
-      <c r="AN4" s="50" t="s">
+      <c r="AQ4" s="48" t="s">
+        <v>45</v>
+      </c>
+      <c r="AR4" s="49" t="s">
         <v>80</v>
       </c>
-      <c r="AO4" s="50" t="s">
+      <c r="AS4" s="49" t="s">
         <v>81</v>
       </c>
-      <c r="AP4" s="50" t="s">
+      <c r="AT4" s="49" t="s">
         <v>82</v>
       </c>
-      <c r="AQ4" s="48" t="s">
-        <v>48</v>
-      </c>
-      <c r="AR4" s="49" t="s">
+      <c r="AU4" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="AS4" s="49" t="s">
+      <c r="AV4" s="49" t="s">
         <v>84</v>
       </c>
-      <c r="AT4" s="49" t="s">
+      <c r="AW4" s="49" t="s">
         <v>85</v>
       </c>
-      <c r="AU4" s="49" t="s">
+      <c r="AX4" s="49" t="s">
         <v>86</v>
       </c>
-      <c r="AV4" s="49" t="s">
+      <c r="AY4" s="49" t="s">
         <v>87</v>
       </c>
-      <c r="AW4" s="49" t="s">
+      <c r="AZ4" s="49" t="s">
         <v>88</v>
       </c>
-      <c r="AX4" s="49" t="s">
+      <c r="BA4" s="49" t="s">
         <v>89</v>
       </c>
-      <c r="AY4" s="49" t="s">
+      <c r="BB4" s="49" t="s">
         <v>90</v>
       </c>
-      <c r="AZ4" s="49" t="s">
+      <c r="BC4" s="48" t="s">
+        <v>45</v>
+      </c>
+      <c r="BD4" s="49" t="s">
         <v>91</v>
       </c>
-      <c r="BA4" s="49" t="s">
+      <c r="BE4" s="49" t="s">
         <v>92</v>
       </c>
-      <c r="BB4" s="49" t="s">
+      <c r="BF4" s="48" t="s">
+        <v>45</v>
+      </c>
+      <c r="BG4" s="50" t="s">
         <v>93</v>
       </c>
-      <c r="BC4" s="48" t="s">
-        <v>48</v>
-      </c>
-      <c r="BD4" s="49" t="s">
+      <c r="BH4" s="49" t="s">
         <v>94</v>
-      </c>
-      <c r="BE4" s="49" t="s">
-        <v>95</v>
-      </c>
-      <c r="BF4" s="48" t="s">
-        <v>48</v>
-      </c>
-      <c r="BG4" s="50" t="s">
-        <v>96</v>
-      </c>
-      <c r="BH4" s="49" t="s">
-        <v>97</v>
       </c>
       <c r="BI4" s="51"/>
     </row>
@@ -3937,14 +3914,14 @@
     <row r="6" s="31" customFormat="1" spans="1:61">
       <c r="A6" s="55"/>
       <c r="B6" s="31" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E6" s="59">
         <f>SUM(E9:E18)</f>
-        <v>2549.4</v>
+        <v>2349.4</v>
       </c>
       <c r="F6" s="60">
         <f t="shared" ref="F6:BI6" si="0">SUM(F9:F18)</f>
@@ -3952,7 +3929,7 @@
       </c>
       <c r="G6" s="60">
         <f t="shared" si="0"/>
-        <v>2549.4</v>
+        <v>2349.4</v>
       </c>
       <c r="H6" s="60">
         <f t="shared" ref="H6:BH6" si="1">SUM(H9:H18)</f>
@@ -3964,7 +3941,7 @@
       </c>
       <c r="J6" s="60">
         <f t="shared" si="1"/>
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="K6" s="60">
         <f t="shared" si="1"/>
@@ -4295,16 +4272,14 @@
     </row>
     <row r="9" s="31" customFormat="1" spans="1:61">
       <c r="A9" s="55"/>
-      <c r="B9" s="31" t="s">
-        <v>99</v>
-      </c>
+      <c r="B9" s="31"/>
       <c r="C9" s="63">
         <f>'China-L'!A2</f>
         <v>0</v>
       </c>
       <c r="E9" s="59">
         <f>SUM(F9:G9)+K9+AQ9+BC9+BF9+BI9</f>
-        <v>2549.4</v>
+        <v>2349.4</v>
       </c>
       <c r="F9" s="60">
         <f>(K9+AQ9+BC9+BF9)*6%</f>
@@ -4312,7 +4287,7 @@
       </c>
       <c r="G9" s="60">
         <f>SUM(H9:J9)</f>
-        <v>2549.4</v>
+        <v>2349.4</v>
       </c>
       <c r="H9" s="60">
         <f>300*PN!$B$29+IF(AN9=0,0,300*PN!$B$29)</f>
@@ -4322,9 +4297,7 @@
         <f>40*PN!$B$29*1</f>
         <v>276.4</v>
       </c>
-      <c r="J9" s="76">
-        <v>200</v>
-      </c>
+      <c r="J9" s="76"/>
       <c r="K9" s="60">
         <f>SUM(L9:AP9)</f>
         <v>0</v>
@@ -5080,7 +5053,7 @@
     <row r="20" ht="13.5"/>
     <row r="21" customFormat="1" ht="14.25" spans="1:61">
       <c r="A21" s="78" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B21" s="79"/>
       <c r="C21" s="79"/>
@@ -5097,7 +5070,7 @@
     <row r="22" customFormat="1" ht="14.25" spans="1:61">
       <c r="A22" s="78"/>
       <c r="B22" s="79" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C22" s="79"/>
       <c r="D22" s="79"/>
@@ -5109,7 +5082,7 @@
     <row r="23" customFormat="1" ht="14.25" spans="1:61">
       <c r="A23" s="78"/>
       <c r="B23" s="79" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C23" s="79"/>
       <c r="D23" s="79"/>
@@ -5121,7 +5094,7 @@
     <row r="24" customFormat="1" ht="14.25" spans="1:61">
       <c r="A24" s="78"/>
       <c r="B24" s="79" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C24" s="79"/>
       <c r="D24" s="79"/>
@@ -5133,7 +5106,7 @@
     <row r="25" customFormat="1" ht="14.25" spans="1:61">
       <c r="A25" s="78"/>
       <c r="B25" s="79" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C25" s="79"/>
       <c r="D25" s="79"/>
@@ -5146,7 +5119,7 @@
     <row r="26" customFormat="1" ht="15" spans="1:61">
       <c r="A26" s="78"/>
       <c r="B26" s="79" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C26" s="79"/>
       <c r="D26" s="79"/>
@@ -5206,10 +5179,9 @@
     <col min="56" max="16384" width="9.09166666666667" style="33"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.5" spans="1:55">
-      <c r="A1" s="32" t="str">
-        <f ca="1">MID(CELL("filename",A1),FIND("]",CELL("filename",A1))+1,256)</f>
-        <v>China EE</v>
+    <row r="1" spans="1:55">
+      <c r="A1" s="32" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="2" ht="13.5" spans="1:55">
@@ -5220,32 +5192,32 @@
       <c r="E2" s="35"/>
       <c r="F2" s="35"/>
       <c r="H2" s="36" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" s="30" customFormat="1" ht="13" customHeight="1" spans="1:55">
       <c r="A3" s="34"/>
       <c r="B3" s="37" t="s">
+        <v>102</v>
+      </c>
+      <c r="C3" s="37" t="s">
+        <v>103</v>
+      </c>
+      <c r="D3" s="37" t="s">
+        <v>104</v>
+      </c>
+      <c r="E3" s="37" t="s">
         <v>105</v>
       </c>
-      <c r="C3" s="37" t="s">
-        <v>106</v>
-      </c>
-      <c r="D3" s="37" t="s">
-        <v>107</v>
-      </c>
-      <c r="E3" s="37" t="s">
-        <v>108</v>
-      </c>
       <c r="F3" s="38" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G3" s="39"/>
       <c r="H3" s="40" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="I3" s="41" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="J3" s="42"/>
       <c r="K3" s="42"/>
@@ -5279,12 +5251,12 @@
       <c r="AM3" s="42"/>
       <c r="AN3" s="42"/>
       <c r="AO3" s="43" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="AP3" s="43"/>
       <c r="AQ3" s="43"/>
       <c r="AR3" s="43" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AS3" s="43"/>
       <c r="AT3" s="43"/>
@@ -5296,10 +5268,10 @@
       <c r="AZ3" s="43"/>
       <c r="BA3" s="43"/>
       <c r="BB3" s="43" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="BC3" s="44" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" s="30" customFormat="1" ht="61" customHeight="1" spans="1:55">
@@ -5308,146 +5280,146 @@
       <c r="D4" s="45"/>
       <c r="E4" s="45"/>
       <c r="F4" s="46" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="G4" s="46" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H4" s="47"/>
       <c r="I4" s="48" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="J4" s="49" t="s">
+        <v>49</v>
+      </c>
+      <c r="K4" s="49" t="s">
+        <v>50</v>
+      </c>
+      <c r="L4" s="49" t="s">
+        <v>51</v>
+      </c>
+      <c r="M4" s="49" t="s">
         <v>52</v>
       </c>
-      <c r="K4" s="49" t="s">
+      <c r="N4" s="49" t="s">
         <v>53</v>
       </c>
-      <c r="L4" s="49" t="s">
+      <c r="O4" s="49" t="s">
         <v>54</v>
       </c>
-      <c r="M4" s="49" t="s">
+      <c r="P4" s="49" t="s">
         <v>55</v>
       </c>
-      <c r="N4" s="49" t="s">
+      <c r="Q4" s="49" t="s">
         <v>56</v>
       </c>
-      <c r="O4" s="49" t="s">
+      <c r="R4" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="P4" s="49" t="s">
+      <c r="S4" s="49" t="s">
         <v>58</v>
       </c>
-      <c r="Q4" s="49" t="s">
+      <c r="T4" s="49" t="s">
         <v>59</v>
       </c>
-      <c r="R4" s="49" t="s">
+      <c r="U4" s="49" t="s">
         <v>60</v>
       </c>
-      <c r="S4" s="49" t="s">
+      <c r="V4" s="49" t="s">
         <v>61</v>
       </c>
-      <c r="T4" s="49" t="s">
+      <c r="W4" s="49" t="s">
         <v>62</v>
       </c>
-      <c r="U4" s="49" t="s">
+      <c r="X4" s="49" t="s">
         <v>63</v>
       </c>
-      <c r="V4" s="49" t="s">
+      <c r="Y4" s="49" t="s">
         <v>64</v>
       </c>
-      <c r="W4" s="49" t="s">
+      <c r="Z4" s="49" t="s">
         <v>65</v>
       </c>
-      <c r="X4" s="49" t="s">
+      <c r="AA4" s="49" t="s">
         <v>66</v>
       </c>
-      <c r="Y4" s="49" t="s">
+      <c r="AB4" s="49" t="s">
         <v>67</v>
       </c>
-      <c r="Z4" s="49" t="s">
+      <c r="AC4" s="49" t="s">
         <v>68</v>
       </c>
-      <c r="AA4" s="49" t="s">
+      <c r="AD4" s="49" t="s">
         <v>69</v>
       </c>
-      <c r="AB4" s="49" t="s">
+      <c r="AE4" s="49" t="s">
         <v>70</v>
       </c>
-      <c r="AC4" s="49" t="s">
+      <c r="AF4" s="49" t="s">
         <v>71</v>
       </c>
-      <c r="AD4" s="49" t="s">
+      <c r="AG4" s="49" t="s">
         <v>72</v>
       </c>
-      <c r="AE4" s="49" t="s">
+      <c r="AH4" s="49" t="s">
         <v>73</v>
       </c>
-      <c r="AF4" s="49" t="s">
+      <c r="AI4" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="AG4" s="49" t="s">
+      <c r="AJ4" s="49" t="s">
         <v>75</v>
       </c>
-      <c r="AH4" s="49" t="s">
+      <c r="AK4" s="49" t="s">
         <v>76</v>
       </c>
-      <c r="AI4" s="49" t="s">
+      <c r="AL4" s="50" t="s">
         <v>77</v>
       </c>
-      <c r="AJ4" s="49" t="s">
+      <c r="AM4" s="49" t="s">
         <v>78</v>
       </c>
-      <c r="AK4" s="49" t="s">
+      <c r="AN4" s="49" t="s">
         <v>79</v>
       </c>
-      <c r="AL4" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="AM4" s="49" t="s">
-        <v>81</v>
-      </c>
-      <c r="AN4" s="49" t="s">
-        <v>82</v>
-      </c>
       <c r="AO4" s="48" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="AP4" s="50" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="AQ4" s="49" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="AR4" s="48" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="AS4" s="49" t="s">
+        <v>113</v>
+      </c>
+      <c r="AT4" s="49" t="s">
+        <v>114</v>
+      </c>
+      <c r="AU4" s="49" t="s">
+        <v>115</v>
+      </c>
+      <c r="AV4" s="49" t="s">
         <v>116</v>
       </c>
-      <c r="AT4" s="49" t="s">
+      <c r="AW4" s="49" t="s">
         <v>117</v>
       </c>
-      <c r="AU4" s="49" t="s">
+      <c r="AX4" s="49" t="s">
         <v>118</v>
       </c>
-      <c r="AV4" s="49" t="s">
+      <c r="AY4" s="49" t="s">
         <v>119</v>
       </c>
-      <c r="AW4" s="49" t="s">
+      <c r="AZ4" s="49" t="s">
         <v>120</v>
       </c>
-      <c r="AX4" s="49" t="s">
-        <v>121</v>
-      </c>
-      <c r="AY4" s="49" t="s">
-        <v>122</v>
-      </c>
-      <c r="AZ4" s="49" t="s">
-        <v>123</v>
-      </c>
       <c r="BA4" s="49" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="BB4" s="48"/>
       <c r="BC4" s="51"/>
@@ -5505,7 +5477,7 @@
     </row>
     <row r="6" s="31" customFormat="1" spans="1:55">
       <c r="A6" s="55" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="H6" s="56"/>
       <c r="I6" s="57"/>
@@ -5717,20 +5689,17 @@
     </row>
     <row r="10" s="31" customFormat="1" spans="1:55">
       <c r="A10" s="55"/>
-      <c r="B10" s="31" t="s">
-        <v>125</v>
-      </c>
-      <c r="C10" s="31" t="str">
+      <c r="B10" s="31"/>
+      <c r="C10" s="31">
         <f>PN!B8</f>
-        <v>Hermetic Solutions Group, Inc</v>
-      </c>
-      <c r="D10" s="63">
-        <f>China!C9</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="31" t="str">
+        <v>0</v>
+      </c>
+      <c r="D10" s="63" t="s">
+        <v>122</v>
+      </c>
+      <c r="E10" s="31">
         <f>China!B9</f>
-        <v>CPT</v>
+        <v>0</v>
       </c>
       <c r="F10" s="64">
         <f ca="1">China!B2</f>
@@ -6494,262 +6463,262 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="36" spans="1:241">
       <c r="A1" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q1" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="R1" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="S1" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="T1" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="U1" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="V1" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="W1" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="X1" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y1" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="Z1" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA1" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="AB1" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC1" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="AD1" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="AE1" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="AF1" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="AG1" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="AH1" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="AI1" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AJ1" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="AK1" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="AL1" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="C1" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="M1" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="N1" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="P1" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q1" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="R1" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="S1" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="T1" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="U1" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="V1" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="W1" s="5" t="s">
+      <c r="AM1" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="AN1" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="AO1" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="AP1" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="AQ1" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="AR1" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="AS1" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="AT1" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="AU1" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="AV1" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="AW1" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="AX1" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="AY1" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="X1" s="5" t="s">
+      <c r="AZ1" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="BA1" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="BB1" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="BC1" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="BD1" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="BE1" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="BF1" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="Y1" s="5" t="s">
+      <c r="BG1" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="BH1" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="BI1" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="BJ1" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="Z1" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="AA1" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="AB1" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="AC1" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="AD1" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="AE1" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="AF1" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="AG1" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="AH1" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="AI1" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="AJ1" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="AK1" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="AL1" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="AM1" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="AN1" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="AO1" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="AP1" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="AQ1" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="AR1" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="AS1" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="AT1" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="AU1" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="AV1" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="AW1" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="AX1" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="AY1" s="5" t="s">
+      <c r="BK1" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AZ1" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="BA1" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="BB1" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="BC1" s="8" t="s">
+      <c r="BL1" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="BM1" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="BN1" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="BD1" s="9" t="s">
+      <c r="BO1" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="BP1" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="BE1" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="BF1" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="BG1" s="8" t="s">
+      <c r="BQ1" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="BR1" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="BH1" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="BI1" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="BJ1" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="BK1" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="BL1" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="BM1" s="5" t="s">
+      <c r="BS1" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="BT1" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="BU1" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="BV1" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="BN1" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="BO1" s="5" t="s">
+      <c r="BW1" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="BP1" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="BQ1" s="5" t="s">
+      <c r="BX1" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="BR1" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="BS1" s="8" t="s">
+      <c r="BY1" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="BZ1" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="CA1" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="CB1" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="CC1" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="CD1" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="BT1" s="8" t="s">
+      <c r="CE1" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="BU1" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="BV1" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="BW1" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="BX1" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="BY1" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="BZ1" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="CA1" s="13" t="s">
+      <c r="CF1" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="CB1" s="13" t="s">
+      <c r="CG1" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="CC1" s="13" t="s">
+      <c r="CK1" s="16" t="s">
         <v>90</v>
-      </c>
-      <c r="CD1" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="CE1" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="CF1" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="CG1" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="CK1" s="16" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="2" s="2" customFormat="1" ht="12" spans="1:241">
